--- a/02_AI_Strategy_and_Roadmap/GT_AI_Opportunity_Discovery_Toolkit_Worked_Example_GT_Bahrain.xlsx
+++ b/02_AI_Strategy_and_Roadmap/GT_AI_Opportunity_Discovery_Toolkit_Worked_Example_GT_Bahrain.xlsx
@@ -31030,7 +31030,7 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="18" customHeight="1">
+    <row r="71" ht="30" customHeight="1">
       <c r="A71" s="4" t="inlineStr">
         <is>
           <t>Value at stake by 2030</t>
@@ -31039,7 +31039,7 @@
       <c r="B71" s="28" t="n"/>
       <c r="C71" s="61" t="str">
         <f>IFERROR(INDEX('7. Sector Profiles'!$B$5:$B$18,MATCH('1. AI Position'!$C$5,'7. Sector Profiles'!$A$5:$A$18,0)),"Select a sector on sheet 1")</f>
-        <v>-</v>
+        <v>Not sized separately in the 2030 analysis - value from audit, tax and advisory delivery (e.g., full-population auditing, predictive tax modelling, DD review)</v>
       </c>
       <c r="D71" s="15" t="n"/>
       <c r="E71" s="15" t="n"/>
@@ -34211,7 +34211,7 @@
       </c>
       <c r="B10" s="61" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Not sized separately in the 2030 analysis - value from faster citizen services, application processing and translation (iGA AI Policy 2025)</t>
         </is>
       </c>
       <c r="C10" s="61" t="inlineStr">
@@ -34421,7 +34421,7 @@
       </c>
       <c r="B16" s="61" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Not sized separately in the 2030 analysis - value from lease administration, tenant service and construction productivity</t>
         </is>
       </c>
       <c r="C16" s="61" t="inlineStr">
@@ -34456,7 +34456,7 @@
       </c>
       <c r="B17" s="61" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Not sized separately in the 2030 analysis - value from student services, content development and timetabling</t>
         </is>
       </c>
       <c r="C17" s="61" t="inlineStr">
@@ -34491,7 +34491,7 @@
       </c>
       <c r="B18" s="61" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Not sized separately in the 2030 analysis - value from audit, tax and advisory delivery (e.g., full-population auditing, predictive tax modelling, DD review)</t>
         </is>
       </c>
       <c r="C18" s="61" t="inlineStr">
@@ -34563,7 +34563,7 @@
     <row r="22" ht="40" customHeight="1">
       <c r="A22" s="62" t="inlineStr">
         <is>
-          <t>Value at stake: QuantumBlack &amp; PwC analysis - predictions for 2030 (as presented in GT Bahrain 'Introduction to Artificial Intelligence', 2026); insurance and capital markets share the financial-services figure; hospitality shares retail &amp; consumer. '-' = no sector figure in that analysis. Potential is GT's qualitative assessment of automation and AI opportunity density in the library.</t>
+          <t>Value at stake: QuantumBlack &amp; PwC analysis - predictions for 2030 (as presented in GT Bahrain 'Introduction to Artificial Intelligence', 2026); insurance and capital markets share the financial-services figure; hospitality shares retail &amp; consumer. Sectors not sized separately in that analysis are described qualitatively. Potential is GT's qualitative assessment of automation and AI opportunity density in the library.</t>
         </is>
       </c>
       <c r="B22" s="15" t="n"/>

--- a/02_AI_Strategy_and_Roadmap/GT_AI_Opportunity_Discovery_Toolkit_Worked_Example_GT_Bahrain.xlsx
+++ b/02_AI_Strategy_and_Roadmap/GT_AI_Opportunity_Discovery_Toolkit_Worked_Example_GT_Bahrain.xlsx
@@ -34563,7 +34563,7 @@
     <row r="22" ht="40" customHeight="1">
       <c r="A22" s="62" t="inlineStr">
         <is>
-          <t>Value at stake: QuantumBlack &amp; PwC analysis - predictions for 2030 (as presented in GT Bahrain 'Introduction to Artificial Intelligence', 2026); insurance and capital markets share the financial-services figure; hospitality shares retail &amp; consumer. Sectors not sized separately in that analysis are described qualitatively. Potential is GT's qualitative assessment of automation and AI opportunity density in the library.</t>
+          <t>Source (value at stake, GDP uplift by 2030): QuantumBlack &amp; PwC analysis (Predictions for 2030); insurance and capital markets share the financial-services figure; hospitality shares retail &amp; consumer. Sectors not sized separately in that analysis are described qualitatively. Potential is GT's qualitative assessment of automation and AI opportunity density in the library.</t>
         </is>
       </c>
       <c r="B22" s="15" t="n"/>

--- a/02_AI_Strategy_and_Roadmap/GT_AI_Opportunity_Discovery_Toolkit_Worked_Example_GT_Bahrain.xlsx
+++ b/02_AI_Strategy_and_Roadmap/GT_AI_Opportunity_Discovery_Toolkit_Worked_Example_GT_Bahrain.xlsx
@@ -2154,7 +2154,7 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>As Medium, plus: AI system impact assessment (ISO/IEC 42005) and DPIA; bias, robustness and security testing (incl. AI red teaming); human-in-the-loop for decisions about individuals; EU AI Act / CBB obligations checked; executive / AI committee approval; GT AI RCM v2.1 controls applied.</t>
+          <t>As Medium, plus: AI system impact assessment (ISO/IEC 42005) and DPIA; bias, robustness and security testing (incl. AI red teaming); human-in-the-loop for decisions about individuals; EU AI Act / CBB obligations checked; executive / AI committee approval; GT AI Risk Assessment Framework controls applied.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -33789,7 +33789,7 @@
       </c>
       <c r="B23" s="69" t="str">
         <f>IFERROR(INDEX(Lists!$AP$2:$AP$4,MATCH(B21,Lists!$AO$2:$AO$4,0)),"")</f>
-        <v>As Medium, plus: AI system impact assessment (ISO/IEC 42005) and DPIA; bias, robustness and security testing (incl. AI red teaming); human-in-the-loop for decisions about individuals; EU AI Act / CBB obligations checked; executive / AI committee approval; GT AI RCM v2.1 controls applied.</v>
+        <v>As Medium, plus: AI system impact assessment (ISO/IEC 42005) and DPIA; bias, robustness and security testing (incl. AI red teaming); human-in-the-loop for decisions about individuals; EU AI Act / CBB obligations checked; executive / AI committee approval; GT AI Risk Assessment Framework controls applied.</v>
       </c>
       <c r="C23" s="15" t="n"/>
       <c r="D23" s="15" t="n"/>
@@ -35293,7 +35293,7 @@
       </c>
       <c r="B40" s="25" t="inlineStr">
         <is>
-          <t>As Medium, plus: AI system impact assessment (ISO/IEC 42005) and DPIA; bias, robustness and security testing (incl. AI red teaming); human-in-the-loop for decisions about individuals; EU AI Act / CBB obligations checked; executive / AI committee approval; GT AI RCM v2.1 controls applied.</t>
+          <t>As Medium, plus: AI system impact assessment (ISO/IEC 42005) and DPIA; bias, robustness and security testing (incl. AI red teaming); human-in-the-loop for decisions about individuals; EU AI Act / CBB obligations checked; executive / AI committee approval; GT AI Risk Assessment Framework controls applied.</t>
         </is>
       </c>
       <c r="C40" s="15" t="n"/>
@@ -35907,7 +35907,7 @@
     <row r="75" ht="40" customHeight="1">
       <c r="A75" s="26" t="inlineStr">
         <is>
-          <t>GT AI Risk Assessment Framework v1.1 and GT AI RCM v2.1</t>
+          <t>GT AI Risk Assessment Framework</t>
         </is>
       </c>
       <c r="B75" s="15" t="n"/>
